--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260811.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260811.xlsx
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>13,347,134</t>
+          <t>1,387,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>1,387,000</t>
+          <t>13,347,134</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>202608WTEQ6F</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>電子指數期貨</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>142,921</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>202608WTEQ6F</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>電子指數期貨</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>142,921</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>1,038,822</t>
+          <t>837,897</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>837,897</t>
+          <t>1,038,822</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>3,340,000</t>
+          <t>389,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>389,000</t>
+          <t>3,340,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>151,386</t>
+          <t>10,987,121</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>10,987,121</t>
+          <t>151,386</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>202608WVHFQ6F</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>404,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>202608WVHFQ6F</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>404,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>804,000</t>
+          <t>96,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>5,140,956</t>
+          <t>804,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>834,000</t>
+          <t>188,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>188,000</t>
+          <t>5,140,956</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>96,000</t>
+          <t>834,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>331,000</t>
+          <t>119,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>1,822,000</t>
+          <t>331,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>119,000</t>
+          <t>1,822,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>263,000</t>
+          <t>162,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>162,000</t>
+          <t>263,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
